--- a/college-posters/data/字段表_211第二批.xlsx
+++ b/college-posters/data/字段表_211第二批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -527,17 +527,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>未核到可靠校友学籍，海报暂显示“校友信息核实中”</t>
+          <t>净月校区：净月潭旁新校区；本部校区：人民大街老校区；图书馆：本部校区标志建筑</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -549,39 +549,39 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>净月校区：净月潭旁新校区；本部校区：人民大街老校区；图书馆：本部校区标志建筑</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>东北师范大学</t>
+          <t>西南交通大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>交通运输、土木工程、车辆工程、电气工程及其自动化、测绘工程、机械工程</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -593,17 +593,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>交通运输、土木工程、车辆工程、电气工程及其自动化、测绘工程、机械工程</t>
+          <t>铁路与轨道交通、土木与桥梁工程、电气与机械制造</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -615,17 +615,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>铁路与轨道交通、土木与桥梁工程、电气与机械制造</t>
+          <t>犀浦校区：成都主校区；九里校区：二环路老校区；峨眉校区：峨眉山下的校区</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -637,39 +637,39 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>犀浦校区：成都主校区；九里校区：二环路老校区；峨眉校区：峨眉山下的校区</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>西南交通大学</t>
+          <t>北京邮电大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>通信工程、计算机科学与技术、电子信息工程、网络空间安全、人工智能、数据科学与大数据技术</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -681,17 +681,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>通信工程、计算机科学与技术、电子信息工程、网络空间安全、人工智能、数据科学与大数据技术</t>
+          <t>通信运营与设备商、互联网与软件、网络安全</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -703,17 +703,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>知名校友</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>通信运营与设备商、互联网与软件、网络安全</t>
+          <t>张平、刘韵洁（北邮校友，院士）</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核（学籍）</t>
         </is>
       </c>
     </row>
@@ -725,17 +725,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>张平、刘韵洁（北邮校友，院士）</t>
+          <t>主楼：海淀校区标志建筑；海淀校区：西土城路主校区；沙河校区：昌平沙河新校区</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核（学籍）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -747,39 +747,39 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>主楼：海淀校区标志建筑；海淀校区：西土城路主校区；沙河校区：昌平沙河新校区</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>北京邮电大学</t>
+          <t>江南大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>食品科学与工程、生物工程、纺织工程、产品设计、化学工程与工艺、物联网工程</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -791,17 +791,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>食品科学与工程、生物工程、纺织工程、产品设计、化学工程与工艺、物联网工程</t>
+          <t>食品与生物企业、轻工与纺织、设计与互联网</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>食品与生物企业、轻工与纺织、设计与互联网</t>
+          <t>蠡湖：校园依蠡湖而建；长广溪湿地：毗邻校园的湿地公园；图书馆：蠡湖校区标志建筑</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -835,39 +835,39 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>蠡湖：校园依蠡湖而建；长广溪湿地：毗邻校园的湿地公园；图书馆：蠡湖校区标志建筑</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>江南大学</t>
+          <t>华中师范大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>软科中国大学排名</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>2026年第53名（单一第三方来源）</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核（仅单一来源）</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>软科中国大学排名</t>
+          <t>第4张排名卡</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2026年第53名（单一第三方来源）</t>
+          <t>双一流1个：中国语言文学（转载名单仅见此一项）；办学123年</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核（仅单一来源）</t>
+          <t>待核教育部名单原文</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>双一流1个：中国语言文学（转载名单仅见此一项）；办学123年</t>
+          <t>汉语言文学、教育学、心理学、历史学、数学与应用数学、计算机科学与技术</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>汉语言文学、教育学、心理学、历史学、数学与应用数学、计算机科学与技术</t>
+          <t>教育与科研、党政机关与事业单位、文化传媒与互联网</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -945,17 +945,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>教育与科研、党政机关与事业单位、文化传媒与互联网</t>
+          <t>桂子山：秋天满山桂花香；博雅广场：校园中心广场；图书馆：桂子山标志建筑</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -967,61 +967,61 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>未核到可靠校友学籍，海报暂显示“校友信息核实中”</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>华中师范大学</t>
+          <t>武汉理工大学</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>桂子山：秋天满山桂花香；博雅广场：校园中心广场；图书馆：桂子山标志建筑</t>
+          <t>材料科学与工程、无机非金属材料工程、车辆工程、船舶与海洋工程、交通运输、计算机科学与技术</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>华中师范大学</t>
+          <t>武汉理工大学</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>建材与新材料、汽车与交通、船舶与物流</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1033,17 +1033,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>材料科学与工程、无机非金属材料工程、车辆工程、船舶与海洋工程、交通运输、计算机科学与技术</t>
+          <t>马房山校区：主校区；南湖校区：南湖畔新校区；余家头校区：长江边的交通校区</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1055,83 +1055,83 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>建材与新材料、汽车与交通、船舶与物流</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>武汉理工大学</t>
+          <t>南京农业大学</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>未核到可靠校友学籍，海报暂显示“校友信息核实中”</t>
+          <t>农学、植物保护、农业资源与环境、园艺、动物医学、食品科学与工程</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>武汉理工大学</t>
+          <t>南京农业大学</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>马房山校区：主校区；南湖校区：南湖畔新校区；余家头校区：长江边的交通校区</t>
+          <t>农业科研院所、食品与生物企业、党政机关与国企</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>武汉理工大学</t>
+          <t>南京农业大学</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>卫岗校区：紫金山下主校区；主楼：大屋顶标志建筑；白马基地：教学科研实践基地</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1143,83 +1143,83 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>农学、植物保护、农业资源与环境、园艺、动物医学、食品科学与工程</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>南京农业大学</t>
+          <t>中国地质大学（武汉）</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>农业科研院所、食品与生物企业、党政机关与国企</t>
+          <t>地质学、资源勘查工程、地球物理学、宝石及材料工艺学、地理信息科学、测绘工程</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>南京农业大学</t>
+          <t>中国地质大学（武汉）</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>卫岗校区：紫金山下主校区；主楼：大屋顶标志建筑；白马基地：教学科研实践基地</t>
+          <t>深造率未查到；B方案改放2023届本科推免（保研）率19.6%（未注明校区）</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核（校区口径不明）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>南京农业大学</t>
+          <t>中国地质大学（武汉）</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>地质勘探与资源、测绘与地理信息、能源与环境</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1231,17 +1231,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>地质学、资源勘查工程、地球物理学、宝石及材料工艺学、地理信息科学、测绘工程</t>
+          <t>逸夫博物馆：地学博物馆，国家4A级景区；南望山校区：主校区；未来城校区：光谷新校区</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1253,83 +1253,83 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>深造率未查到；B方案改放2023届本科推免（保研）率19.6%（未注明校区）</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>待核（校区口径不明）</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>中国地质大学（武汉）</t>
+          <t>北京化工大学</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>地质勘探与资源、测绘与地理信息、能源与环境</t>
+          <t>化学工程与工艺、高分子材料与工程、应用化学、生物工程、材料科学与工程、自动化</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>中国地质大学（武汉）</t>
+          <t>北京化工大学</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>逸夫博物馆：地学博物馆，国家4A级景区；南望山校区：主校区；未来城校区：光谷新校区</t>
+          <t>石油化工与能源、新材料、生物医药</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>中国地质大学（武汉）</t>
+          <t>北京化工大学</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>东校区：朝阳区主校区；北校区：朝阳区校区；昌平校区：新建校区</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1341,68 +1341,68 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>化学工程与工艺、高分子材料与工程、应用化学、生物工程、材料科学与工程、自动化</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>北京化工大学</t>
+          <t>南京师范大学</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>石油化工与能源、新材料、生物医药</t>
+          <t>汉语言文学、地理科学、教育学、心理学、数学与应用数学、法学</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>北京化工大学</t>
+          <t>南京师范大学</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>未核到可靠校友学籍，海报暂显示“校友信息核实中”</t>
+          <t>教育与科研、党政机关与事业单位、文化传媒</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>待补</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>北京化工大学</t>
+          <t>南京师范大学</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>东校区：朝阳区主校区；北校区：朝阳区校区；昌平校区：新建校区</t>
+          <t>随园校区：中西合璧的大屋顶建筑群；仙林校区：主校区；紫金校区：新校区</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>北京化工大学</t>
+          <t>南京师范大学</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1438,116 +1438,6 @@
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>南京师范大学</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>汉语言文学、地理科学、教育学、心理学、数学与应用数学、法学</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>南京师范大学</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>教育与科研、党政机关与事业单位、文化传媒</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>南京师范大学</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>知名校友</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>未核到可靠校友学籍，海报暂显示“校友信息核实中”</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>南京师范大学</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>随园校区：中西合璧的大屋顶建筑群；仙林校区：主校区；紫金校区：新校区</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>南京师范大学</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>待核2027年招生章程</t>
         </is>
@@ -2127,27 +2017,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>特色亮点（替代知名校友）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>未核到可靠校友学籍，海报暂显示“校友信息核实中”</t>
+          <t>国家重点实验室：化工资源有效利用国家重点实验室；国家重点实验室：有机无机复合材料国家重点实验室；行业特色：石化行业人才的重要输送地</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>校友信息核实中</t>
+          <t>国家重点实验室 化工资源有效利用国家重点实验室；国家重点实验室 有机无机复合材料国家重点实验室；行业特色 石化行业人才的重要输送地</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
+          <t>学校官网、公开资料</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>较可靠，待核官网介绍（用户选B：无可靠校友时改放特色亮点）</t>
         </is>
       </c>
     </row>
@@ -2885,27 +2775,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>特色亮点（替代知名校友）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>未核到可靠校友学籍，海报暂显示“校友信息核实中”</t>
+          <t>金陵女子大学旧址：随园建筑群，全国重点文物保护单位；地理学：虚拟地理环境教育部重点实验室；教师教育：江苏基础教育师资重要来源</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>校友信息核实中</t>
+          <t>金陵女子大学旧址 随园建筑群，全国重点文物保护单位；地理学 虚拟地理环境教育部重点实验室；教师教育 江苏基础教育师资重要来源</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
+          <t>学校官网、公开资料</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>较可靠，待核官网介绍（用户选B：无可靠校友时改放特色亮点）</t>
         </is>
       </c>
     </row>
@@ -3643,27 +3533,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>特色亮点（替代知名校友）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>未核到可靠校友学籍，海报暂显示“校友信息核实中”</t>
+          <t>部属师范大学：全国6所教育部直属师范大学之一；公费师范生：2007年起首批实施免费师范教育；净月校区：毗邻净月潭国家森林公园</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>校友信息核实中</t>
+          <t>部属师范大学 全国6所教育部直属师范大学之一；公费师范生 2007年起首批实施免费师范教育；净月校区 毗邻净月潭国家森林公园</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
+          <t>学校官网、公开资料</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>较可靠，待核官网介绍（用户选B：无可靠校友时改放特色亮点）</t>
         </is>
       </c>
     </row>
@@ -6675,27 +6565,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>特色亮点（替代知名校友）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>未核到可靠校友学籍，海报暂显示“校友信息核实中”</t>
+          <t>部属师范大学：全国6所教育部直属师范大学之一；公费师范生：2007年起首批实施免费师范教育；数字化学习：国家数字化学习工程技术研究中心</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>校友信息核实中</t>
+          <t>部属师范大学 全国6所教育部直属师范大学之一；公费师范生 2007年起首批实施免费师范教育；数字化学习 国家数字化学习工程技术研究中心</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
+          <t>学校官网、公开资料</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>较可靠，待核官网介绍（用户选B：无可靠校友时改放特色亮点）</t>
         </is>
       </c>
     </row>
@@ -7433,27 +7323,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>特色亮点（替代知名校友）</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>未核到可靠校友学籍，海报暂显示“校友信息核实中”</t>
+          <t>三校合并：武汉工大、交通科大、汽车工大；国家重点实验室：硅酸盐建筑材料国家重点实验室；国家重点实验室：材料复合新技术国家重点实验室</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>校友信息核实中</t>
+          <t>三校合并 武汉工大、交通科大、汽车工大；国家重点实验室 硅酸盐建筑材料国家重点实验室；国家重点实验室 材料复合新技术国家重点实验室</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待补</t>
+          <t>学校官网、公开资料</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>较可靠，待核官网介绍（用户选B：无可靠校友时改放特色亮点）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/字段表_211第二批.xlsx
+++ b/college-posters/data/字段表_211第二批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,68 +505,68 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>教育与科研、党政机关与事业单位、文化与传媒</t>
+          <t>净月校区：净月潭旁新校区；本部校区：人民大街老校区；图书馆：本部校区标志建筑</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>东北师范大学</t>
+          <t>西南交通大学</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>净月校区：净月潭旁新校区；本部校区：人民大街老校区；图书馆：本部校区标志建筑</t>
+          <t>交通运输、土木工程、车辆工程、电气工程及其自动化、测绘工程、机械工程</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>东北师范大学</t>
+          <t>西南交通大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>犀浦校区：成都主校区；九里校区：二环路老校区；峨眉校区：峨眉山下的校区</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>西南交通大学</t>
+          <t>北京邮电大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>交通运输、土木工程、车辆工程、电气工程及其自动化、测绘工程、机械工程</t>
+          <t>通信工程、计算机科学与技术、电子信息工程、网络空间安全、人工智能、数据科学与大数据技术</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -588,183 +588,183 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>西南交通大学</t>
+          <t>北京邮电大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>铁路与轨道交通、土木与桥梁工程、电气与机械制造</t>
+          <t>主楼：海淀校区标志建筑；海淀校区：西土城路主校区；沙河校区：昌平沙河新校区</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>西南交通大学</t>
+          <t>江南大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>犀浦校区：成都主校区；九里校区：二环路老校区；峨眉校区：峨眉山下的校区</t>
+          <t>食品科学与工程、生物工程、纺织工程、产品设计、化学工程与工艺、物联网工程</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>西南交通大学</t>
+          <t>江南大学</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>蠡湖：校园依蠡湖而建；长广溪湿地：毗邻校园的湿地公园；图书馆：蠡湖校区标志建筑</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>北京邮电大学</t>
+          <t>华中师范大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>软科中国大学排名</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>通信工程、计算机科学与技术、电子信息工程、网络空间安全、人工智能、数据科学与大数据技术</t>
+          <t>2026年第53名（单一第三方来源）</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核（仅单一来源）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>北京邮电大学</t>
+          <t>华中师范大学</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>通信运营与设备商、互联网与软件、网络安全</t>
+          <t>汉语言文学、教育学、心理学、历史学、数学与应用数学、计算机科学与技术</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>北京邮电大学</t>
+          <t>华中师范大学</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>张平、刘韵洁（北邮校友，院士）</t>
+          <t>桂子山：秋天满山桂花香；博雅广场：校园中心广场；图书馆：桂子山标志建筑</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核（学籍）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>北京邮电大学</t>
+          <t>武汉理工大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>主楼：海淀校区标志建筑；海淀校区：西土城路主校区；沙河校区：昌平沙河新校区</t>
+          <t>材料科学与工程、无机非金属材料工程、车辆工程、船舶与海洋工程、交通运输、计算机科学与技术</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>北京邮电大学</t>
+          <t>武汉理工大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>马房山校区：主校区；南湖校区：南湖畔新校区；余家头校区：长江边的交通校区</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>江南大学</t>
+          <t>南京农业大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>食品科学与工程、生物工程、纺织工程、产品设计、化学工程与工艺、物联网工程</t>
+          <t>农学、植物保护、农业资源与环境、园艺、动物医学、食品科学与工程</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -786,161 +786,161 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>江南大学</t>
+          <t>南京农业大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>食品与生物企业、轻工与纺织、设计与互联网</t>
+          <t>卫岗校区：紫金山下主校区；主楼：大屋顶标志建筑；白马基地：教学科研实践基地</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>江南大学</t>
+          <t>中国地质大学（武汉）</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>蠡湖：校园依蠡湖而建；长广溪湿地：毗邻校园的湿地公园；图书馆：蠡湖校区标志建筑</t>
+          <t>地质学、资源勘查工程、地球物理学、宝石及材料工艺学、地理信息科学、测绘工程</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>江南大学</t>
+          <t>中国地质大学（武汉）</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>深造率未查到；B方案改放2023届本科推免（保研）率19.6%（未注明校区）</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核（校区口径不明）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>华中师范大学</t>
+          <t>中国地质大学（武汉）</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>软科中国大学排名</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2026年第53名（单一第三方来源）</t>
+          <t>逸夫博物馆：地学博物馆，国家4A级景区；南望山校区：主校区；未来城校区：光谷新校区</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核（仅单一来源）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>华中师范大学</t>
+          <t>北京化工大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>双一流1个：中国语言文学（转载名单仅见此一项）；办学123年</t>
+          <t>化学工程与工艺、高分子材料与工程、应用化学、生物工程、材料科学与工程、自动化</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>华中师范大学</t>
+          <t>北京化工大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>汉语言文学、教育学、心理学、历史学、数学与应用数学、计算机科学与技术</t>
+          <t>东校区：朝阳区主校区；北校区：朝阳区校区；昌平校区：新建校区</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>华中师范大学</t>
+          <t>南京师范大学</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>教育与科研、党政机关与事业单位、文化传媒与互联网</t>
+          <t>汉语言文学、地理科学、教育学、心理学、数学与应用数学、法学</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>华中师范大学</t>
+          <t>南京师范大学</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -950,496 +950,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>桂子山：秋天满山桂花香；博雅广场：校园中心广场；图书馆：桂子山标志建筑</t>
+          <t>随园校区：中西合璧的大屋顶建筑群；仙林校区：主校区；紫金校区：新校区</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>华中师范大学</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>武汉理工大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>材料科学与工程、无机非金属材料工程、车辆工程、船舶与海洋工程、交通运输、计算机科学与技术</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>武汉理工大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>建材与新材料、汽车与交通、船舶与物流</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>武汉理工大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>马房山校区：主校区；南湖校区：南湖畔新校区；余家头校区：长江边的交通校区</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>武汉理工大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>南京农业大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>农学、植物保护、农业资源与环境、园艺、动物医学、食品科学与工程</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>南京农业大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>农业科研院所、食品与生物企业、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>南京农业大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>卫岗校区：紫金山下主校区；主楼：大屋顶标志建筑；白马基地：教学科研实践基地</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>南京农业大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>中国地质大学（武汉）</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>地质学、资源勘查工程、地球物理学、宝石及材料工艺学、地理信息科学、测绘工程</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>中国地质大学（武汉）</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>深造率</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>深造率未查到；B方案改放2023届本科推免（保研）率19.6%（未注明校区）</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核（校区口径不明）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>中国地质大学（武汉）</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>地质勘探与资源、测绘与地理信息、能源与环境</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>中国地质大学（武汉）</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>逸夫博物馆：地学博物馆，国家4A级景区；南望山校区：主校区；未来城校区：光谷新校区</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>中国地质大学（武汉）</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>北京化工大学</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>化学工程与工艺、高分子材料与工程、应用化学、生物工程、材料科学与工程、自动化</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>北京化工大学</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>石油化工与能源、新材料、生物医药</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>北京化工大学</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>东校区：朝阳区主校区；北校区：朝阳区校区；昌平校区：新建校区</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>北京化工大学</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>南京师范大学</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>汉语言文学、地理科学、教育学、心理学、数学与应用数学、法学</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>南京师范大学</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>教育与科研、党政机关与事业单位、文化传媒</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>南京师范大学</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>随园校区：中西合璧的大屋顶建筑群；仙林校区：主校区；紫金校区：新校区</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>南京师范大学</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -2003,9 +1519,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2128,12 +1644,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2761,9 +2277,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2886,12 +2402,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3519,9 +3035,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3160,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4277,9 +3793,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4402,12 +3918,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5035,9 +4551,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5054,12 +4570,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>张平、刘韵洁（北邮校友，院士）</t>
+          <t>张平（北邮校友）；刘韵洁毕业于北京大学，非北邮校友，已撤下</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>张平 中国工程院院士；刘韵洁 中国工程院院士</t>
+          <t>张平 中国工程院院士</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -5067,9 +4583,9 @@
           <t>学校官网、权威媒体</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（学籍）</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>已核（已更正）</t>
         </is>
       </c>
     </row>
@@ -5160,12 +4676,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5793,9 +5309,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5918,12 +5434,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6314,22 +5830,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>双一流1个：中国语言文学（转载名单仅见此一项）；办学123年</t>
+          <t>双一流3个：政治学、教育学、中国语言文学；初稿只写1个，已更正</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1个；123年</t>
+          <t>3个；123年</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>教育部 教研函〔2022〕1号 名单（转载）</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+          <t>中国日报、大学生必备网（多源一致）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核（已更正）</t>
         </is>
       </c>
     </row>
@@ -6378,12 +5894,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>中国语言文学</t>
+          <t>政治学、教育学、中国语言文学</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>中国语言文学</t>
+          <t>政治学、教育学、中国语言文学</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6393,7 +5909,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>已核（海报取其中6个）</t>
+          <t>已核（已更正）</t>
         </is>
       </c>
     </row>
@@ -6410,12 +5926,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>中文、教育学等学科优势突出</t>
+          <t>政治学、教育学、中国语言文学为国家双一流建设学科</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>中文、教育学等学科优势突出</t>
+          <t>政治学、教育学、中国语言文学为国家双一流建设学科</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -6551,9 +6067,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6086,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>部属师范大学：全国6所教育部直属师范大学之一；公费师范生：2007年起首批实施免费师范教育；数字化学习：国家数字化学习工程技术研究中心</t>
+          <t>部属师范大学：全国6所教育部直属师范大学之一；公费师范生：2007年起首批实施免费师范教育；双一流学科：政治学、教育学、中国语言文学</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>部属师范大学 全国6所教育部直属师范大学之一；公费师范生 2007年起首批实施免费师范教育；数字化学习 国家数字化学习工程技术研究中心</t>
+          <t>部属师范大学 全国6所教育部直属师范大学之一；公费师范生 2007年起首批实施免费师范教育；双一流学科 政治学、教育学、中国语言文学</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6676,12 +6192,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7309,9 +6825,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -7434,12 +6950,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8067,9 +7583,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8192,12 +7708,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8825,9 +8341,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8950,12 +8466,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
